--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2018_T4_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2018_T4_0.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="50">
   <si>
     <t/>
   </si>
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>86</t>
+    <t>82</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.314</t>
-  </si>
-  <si>
-    <t>(0.050)</t>
-  </si>
-  <si>
-    <t>0.477</t>
-  </si>
-  <si>
-    <t>(0.054)</t>
-  </si>
-  <si>
-    <t>0.256</t>
-  </si>
-  <si>
-    <t>(0.047)</t>
-  </si>
-  <si>
-    <t>0.895</t>
-  </si>
-  <si>
-    <t>(0.256)</t>
-  </si>
-  <si>
-    <t>1.233</t>
-  </si>
-  <si>
-    <t>(0.214)</t>
-  </si>
-  <si>
-    <t>0.384</t>
-  </si>
-  <si>
-    <t>(0.089)</t>
+    <t>0.329</t>
+  </si>
+  <si>
+    <t>(0.052)</t>
+  </si>
+  <si>
+    <t>0.500</t>
+  </si>
+  <si>
+    <t>(0.056)</t>
+  </si>
+  <si>
+    <t>0.268</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>0.939</t>
+  </si>
+  <si>
+    <t>(0.268)</t>
+  </si>
+  <si>
+    <t>1.293</t>
+  </si>
+  <si>
+    <t>(0.223)</t>
+  </si>
+  <si>
+    <t>0.402</t>
+  </si>
+  <si>
+    <t>(0.093)</t>
   </si>
   <si>
     <t>28</t>
@@ -102,9 +102,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>0.500</t>
-  </si>
-  <si>
     <t>(0.096)</t>
   </si>
   <si>
@@ -138,7 +135,7 @@
     <t>(0.264)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -150,22 +147,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.186*</t>
-  </si>
-  <si>
-    <t>0.309***</t>
-  </si>
-  <si>
-    <t>0.458***</t>
-  </si>
-  <si>
-    <t>1.069</t>
-  </si>
-  <si>
-    <t>2.017***</t>
-  </si>
-  <si>
-    <t>1.045***</t>
+    <t>0.171</t>
+  </si>
+  <si>
+    <t>0.286***</t>
+  </si>
+  <si>
+    <t>0.446***</t>
+  </si>
+  <si>
+    <t>1.025</t>
+  </si>
+  <si>
+    <t>1.957***</t>
+  </si>
+  <si>
+    <t>1.026***</t>
   </si>
 </sst>
 </file>
@@ -232,7 +229,7 @@
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
@@ -255,7 +252,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -278,7 +275,7 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -295,13 +292,13 @@
         <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -318,7 +315,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -341,13 +338,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -364,7 +361,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
@@ -387,13 +384,13 @@
         <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -410,7 +407,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
@@ -433,13 +430,13 @@
         <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -456,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
@@ -479,13 +476,13 @@
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -502,7 +499,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
@@ -525,13 +522,13 @@
         <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -548,7 +545,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
